--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
+  </si>
+  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
-  </si>
-  <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -239,73 +239,88 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -317,28 +332,13 @@
     <t>DANA PAOLA</t>
   </si>
   <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -849,22 +849,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -885,7 +885,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -897,7 +897,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -926,22 +926,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -962,7 +962,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -971,13 +971,13 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1003,22 +1003,22 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1039,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1048,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1080,22 +1080,22 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1116,22 +1116,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1157,22 +1157,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1205,10 +1205,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1234,22 +1234,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1273,7 +1273,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1311,22 +1311,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1350,19 +1350,19 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1388,22 +1388,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1465,22 +1465,22 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1501,7 +1501,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1510,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1542,22 +1542,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1619,22 +1619,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1670,7 +1670,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1696,22 +1696,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1732,22 +1732,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1773,22 +1773,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1824,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1832,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1850,22 +1850,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1886,7 +1886,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -1895,13 +1895,13 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1927,22 +1927,22 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1963,7 +1963,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2004,22 +2004,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2040,7 +2040,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2049,13 +2049,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2081,22 +2081,22 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2117,10 +2117,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2129,10 +2129,10 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2158,22 +2158,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2194,10 +2194,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2206,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2235,22 +2235,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2274,19 +2274,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2312,22 +2312,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2351,16 +2351,16 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2389,22 +2389,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2428,7 +2428,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2466,22 +2466,22 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2543,22 +2543,22 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2582,13 +2582,13 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2620,22 +2620,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2659,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2668,10 +2668,10 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2697,22 +2697,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2733,10 +2733,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2774,22 +2774,22 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2819,10 +2819,10 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2851,22 +2851,22 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2890,7 +2890,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -2928,22 +2928,22 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2967,7 +2967,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3005,22 +3005,22 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3082,22 +3082,22 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3133,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3159,22 +3159,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3210,7 +3210,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3236,22 +3236,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3313,22 +3313,22 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3352,19 +3352,19 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>6</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3390,22 +3390,22 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3429,7 +3429,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3438,10 +3438,10 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3467,22 +3467,22 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3515,10 +3515,10 @@
         <v>10</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3544,22 +3544,22 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3583,7 +3583,7 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>8</v>
@@ -3595,7 +3595,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3621,22 +3621,22 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3657,7 +3657,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3669,10 +3669,10 @@
         <v>10</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3698,22 +3698,22 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3734,7 +3734,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U41">
         <v>9</v>
@@ -3743,13 +3743,13 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3775,22 +3775,22 @@
         <v>9</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3814,7 +3814,7 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -3852,22 +3852,22 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J43">
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3888,7 +3888,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U43">
         <v>6</v>
@@ -4039,16 +4039,16 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4057,16 +4057,16 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4098,16 +4098,16 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J5">
         <v>82.59999999999999</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4116,16 +4116,16 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5">
         <v>82.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4157,10 +4157,10 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I6">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J6">
         <v>82.59999999999999</v>
@@ -4169,16 +4169,16 @@
         <v>92</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P6">
         <v>82.59999999999999</v>
@@ -4187,10 +4187,10 @@
         <v>92</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4219,37 +4219,37 @@
         <v>95</v>
       </c>
       <c r="I7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J7">
         <v>82.59999999999999</v>
       </c>
       <c r="K7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N7">
         <v>95</v>
       </c>
       <c r="O7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P7">
         <v>82.59999999999999</v>
       </c>
       <c r="Q7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4275,7 +4275,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -4284,16 +4284,16 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4302,13 +4302,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4334,17 +4334,17 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I9">
+        <v>98</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>96</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-      <c r="K9">
-        <v>92</v>
-      </c>
       <c r="L9">
         <v>100</v>
       </c>
@@ -4352,16 +4352,16 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O9">
+        <v>98</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
         <v>96</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9">
-        <v>92</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4393,7 +4393,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4411,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4511,40 +4511,40 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4570,7 +4570,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4588,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4632,13 +4632,13 @@
         <v>90</v>
       </c>
       <c r="I14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4650,13 +4650,13 @@
         <v>90</v>
       </c>
       <c r="O14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4688,37 +4688,37 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4750,7 +4750,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4768,7 +4768,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4806,16 +4806,16 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J17">
         <v>82.59999999999999</v>
       </c>
       <c r="K17">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4824,16 +4824,16 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P17">
         <v>82.59999999999999</v>
       </c>
       <c r="Q17">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4868,13 +4868,13 @@
         <v>85</v>
       </c>
       <c r="I18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4886,13 +4886,13 @@
         <v>85</v>
       </c>
       <c r="O18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4924,7 +4924,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4933,16 +4933,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4951,13 +4951,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4983,10 +4983,10 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I20">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -5001,10 +5001,10 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O20">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -5042,17 +5042,17 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="I21">
+        <v>98</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>96</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>92</v>
-      </c>
       <c r="L21">
         <v>100</v>
       </c>
@@ -5060,16 +5060,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="O21">
+        <v>98</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
         <v>96</v>
-      </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
-      <c r="Q21">
-        <v>92</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5101,10 +5101,10 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -5119,10 +5119,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5160,40 +5160,40 @@
         <v>100</v>
       </c>
       <c r="H23">
+        <v>87.5</v>
+      </c>
+      <c r="I23">
+        <v>98</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
         <v>90</v>
       </c>
-      <c r="I23">
-        <v>96</v>
-      </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
-      <c r="K23">
-        <v>96</v>
-      </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N23">
+        <v>87.5</v>
+      </c>
+      <c r="O23">
+        <v>98</v>
+      </c>
+      <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
         <v>90</v>
       </c>
-      <c r="O23">
-        <v>96</v>
-      </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>96</v>
-      </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5222,37 +5222,37 @@
         <v>85</v>
       </c>
       <c r="I24">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J24">
         <v>78.3</v>
       </c>
       <c r="K24">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N24">
         <v>85</v>
       </c>
       <c r="O24">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="P24">
         <v>78.3</v>
       </c>
       <c r="Q24">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5278,7 +5278,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5287,16 +5287,16 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N25">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5305,13 +5305,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5337,40 +5337,40 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="I26">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J26">
         <v>78.3</v>
       </c>
       <c r="K26">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N26">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="O26">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="P26">
         <v>78.3</v>
       </c>
       <c r="Q26">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5396,7 +5396,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5405,16 +5405,16 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5423,13 +5423,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5455,16 +5455,16 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I28">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J28">
         <v>78.3</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5473,16 +5473,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O28">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="P28">
         <v>78.3</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5517,37 +5517,37 @@
         <v>85</v>
       </c>
       <c r="I29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J29">
         <v>78.3</v>
       </c>
       <c r="K29">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N29">
         <v>85</v>
       </c>
       <c r="O29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P29">
         <v>78.3</v>
       </c>
       <c r="Q29">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5573,40 +5573,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="I30">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J30">
         <v>78.3</v>
       </c>
       <c r="K30">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N30">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="O30">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="P30">
         <v>78.3</v>
       </c>
       <c r="Q30">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5632,40 +5632,40 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N31">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="O31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5691,40 +5691,40 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I32">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J32">
         <v>78.3</v>
       </c>
       <c r="K32">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N32">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="O32">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="P32">
         <v>78.3</v>
       </c>
       <c r="Q32">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5750,7 +5750,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5765,10 +5765,10 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5783,7 +5783,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5809,7 +5809,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -5818,7 +5818,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5827,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5836,7 +5836,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5868,10 +5868,10 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I35">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5886,10 +5886,10 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O35">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5930,37 +5930,37 @@
         <v>85</v>
       </c>
       <c r="I36">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M36">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N36">
         <v>85</v>
       </c>
       <c r="O36">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P36">
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5995,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6013,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -6104,7 +6104,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -6113,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6122,7 +6122,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -6131,7 +6131,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6175,7 +6175,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -6193,7 +6193,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -6222,7 +6222,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -6234,13 +6234,13 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M41">
         <v>100</v>
       </c>
       <c r="N41">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6252,7 +6252,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6281,10 +6281,10 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J42">
         <v>100</v>
@@ -6299,10 +6299,10 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P42">
         <v>100</v>
@@ -6340,40 +6340,40 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I43">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J43">
         <v>78.3</v>
       </c>
       <c r="K43">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L43">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M43">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N43">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O43">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P43">
         <v>78.3</v>
       </c>
       <c r="Q43">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R43">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S43">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6471,19 +6471,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6503,30 +6503,30 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -6547,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6627,7 +6627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6654,26 +6654,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920212</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6681,7 +6661,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6713,39 +6693,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920212</v>
+        <v>22330051920333</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2">
         <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2">
-        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920212</v>
+        <v>22330051920053</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6759,22 +6739,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920359</v>
+        <v>22330051920054</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6782,16 +6762,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920359</v>
+        <v>22330051920061</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6805,22 +6785,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6828,16 +6808,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920237</v>
+        <v>22330051920064</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6851,22 +6831,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920071</v>
+        <v>21330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6874,16 +6854,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920071</v>
+        <v>21330051920237</v>
       </c>
       <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -6897,22 +6877,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920053</v>
+        <v>22330051920071</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6920,16 +6900,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920053</v>
+        <v>22330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6943,22 +6923,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920242</v>
+        <v>21330051920053</v>
       </c>
       <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6969,13 +6949,13 @@
         <v>21330051920242</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -6989,16 +6969,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920333</v>
+        <v>22330051920084</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7007,144 +6987,6 @@
         <v>64</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920053</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920054</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920061</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920064</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920218</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920084</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -212,7 +212,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
     <t>Ramírez Vargas Miranda Alejandra</t>

--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -239,60 +239,36 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -305,22 +281,7 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -855,7 +816,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -891,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -932,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -968,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1009,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -1045,7 +1006,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1086,7 +1047,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1122,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1163,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1240,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1317,7 +1278,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1353,7 +1314,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1394,7 +1355,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1430,7 +1391,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1471,7 +1432,7 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -1507,7 +1468,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1548,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1625,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1661,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1702,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -1738,7 +1699,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1779,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1856,7 +1817,7 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -1933,7 +1894,7 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -2010,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -2046,7 +2007,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2087,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2123,7 +2084,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2164,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -2200,7 +2161,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2241,7 +2202,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -2318,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>8</v>
@@ -2354,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2395,7 +2356,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -2472,7 +2433,7 @@
         <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2549,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2626,7 +2587,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -2703,7 +2664,7 @@
         <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -2780,7 +2741,7 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -2857,7 +2818,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -2934,7 +2895,7 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -2970,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3011,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -3088,7 +3049,7 @@
         <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -3165,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -3201,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3242,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>10</v>
@@ -3319,7 +3280,7 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>7</v>
@@ -3355,7 +3316,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -3396,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
         <v>10</v>
@@ -3432,7 +3393,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3473,7 +3434,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>10</v>
@@ -3509,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3550,7 +3511,7 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -3586,7 +3547,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>9</v>
@@ -3627,7 +3588,7 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -3704,7 +3665,7 @@
         <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>10</v>
@@ -3740,7 +3701,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -3781,7 +3742,7 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>10</v>
@@ -3817,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W42">
         <v>10</v>
@@ -3858,7 +3819,7 @@
         <v>6</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>7</v>
@@ -4104,7 +4065,7 @@
         <v>98</v>
       </c>
       <c r="J5">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K5">
         <v>90</v>
@@ -4122,7 +4083,7 @@
         <v>98</v>
       </c>
       <c r="P5">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q5">
         <v>90</v>
@@ -4163,7 +4124,7 @@
         <v>96</v>
       </c>
       <c r="J6">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="K6">
         <v>92</v>
@@ -4181,7 +4142,7 @@
         <v>96</v>
       </c>
       <c r="P6">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q6">
         <v>92</v>
@@ -4222,7 +4183,7 @@
         <v>98</v>
       </c>
       <c r="J7">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K7">
         <v>96</v>
@@ -4240,7 +4201,7 @@
         <v>98</v>
       </c>
       <c r="P7">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q7">
         <v>96</v>
@@ -4812,7 +4773,7 @@
         <v>96</v>
       </c>
       <c r="J17">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K17">
         <v>84</v>
@@ -4830,7 +4791,7 @@
         <v>96</v>
       </c>
       <c r="P17">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q17">
         <v>84</v>
@@ -4930,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="K19">
         <v>96</v>
@@ -4948,7 +4909,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q19">
         <v>96</v>
@@ -5225,7 +5186,7 @@
         <v>86</v>
       </c>
       <c r="J24">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K24">
         <v>88</v>
@@ -5243,7 +5204,7 @@
         <v>86</v>
       </c>
       <c r="P24">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q24">
         <v>88</v>
@@ -5343,7 +5304,7 @@
         <v>86</v>
       </c>
       <c r="J26">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K26">
         <v>88</v>
@@ -5361,7 +5322,7 @@
         <v>86</v>
       </c>
       <c r="P26">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q26">
         <v>88</v>
@@ -5461,7 +5422,7 @@
         <v>92</v>
       </c>
       <c r="J28">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K28">
         <v>92</v>
@@ -5479,7 +5440,7 @@
         <v>92</v>
       </c>
       <c r="P28">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q28">
         <v>92</v>
@@ -5520,7 +5481,7 @@
         <v>98</v>
       </c>
       <c r="J29">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K29">
         <v>94</v>
@@ -5538,7 +5499,7 @@
         <v>98</v>
       </c>
       <c r="P29">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q29">
         <v>94</v>
@@ -5579,7 +5540,7 @@
         <v>92</v>
       </c>
       <c r="J30">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K30">
         <v>88</v>
@@ -5597,7 +5558,7 @@
         <v>92</v>
       </c>
       <c r="P30">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q30">
         <v>88</v>
@@ -5697,7 +5658,7 @@
         <v>86</v>
       </c>
       <c r="J32">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K32">
         <v>82</v>
@@ -5715,7 +5676,7 @@
         <v>86</v>
       </c>
       <c r="P32">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q32">
         <v>82</v>
@@ -5756,7 +5717,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="K33">
         <v>92</v>
@@ -5774,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q33">
         <v>92</v>
@@ -6346,7 +6307,7 @@
         <v>98</v>
       </c>
       <c r="J43">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="K43">
         <v>82</v>
@@ -6364,7 +6325,7 @@
         <v>98</v>
       </c>
       <c r="P43">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="Q43">
         <v>82</v>
@@ -6439,19 +6400,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>67.5</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>32.5</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6661,7 +6622,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6693,16 +6654,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920333</v>
+        <v>22330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6716,7 +6677,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920053</v>
+        <v>21330051920359</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
@@ -6725,7 +6686,7 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6739,16 +6700,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920054</v>
+        <v>21330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6762,16 +6723,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920061</v>
+        <v>22330051920071</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6785,16 +6746,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920212</v>
+        <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6808,16 +6769,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920064</v>
+        <v>21330051920053</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6831,16 +6792,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920359</v>
+        <v>21330051920242</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6854,16 +6815,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920237</v>
+        <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -6872,121 +6833,6 @@
         <v>64</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920071</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920218</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920053</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920242</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920084</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="111">
   <si>
     <t>Materia</t>
   </si>
@@ -80,6 +80,9 @@
     <t>CRUZ FELIPE ELIDA CITLALI</t>
   </si>
   <si>
+    <t>FLORES CARRERA MONSERRAT</t>
+  </si>
+  <si>
     <t>GARCIA PALACIOS JOCELYN</t>
   </si>
   <si>
@@ -116,12 +119,18 @@
     <t>JUAREZ SILVA HANNY YUSETH</t>
   </si>
   <si>
+    <t>LEYVA VELASQUEZ ESTRELLA</t>
+  </si>
+  <si>
     <t>LOPEZ MARTINEZ EDUARDO</t>
   </si>
   <si>
     <t>MACHORRO ROMERO JIMENA</t>
   </si>
   <si>
+    <t>MARCELINO LOBATO MARIA ELISA</t>
+  </si>
+  <si>
     <t>MARTINEZ HERNANDEZ DIEGO ANTONIO</t>
   </si>
   <si>
@@ -149,6 +158,9 @@
     <t>RAMIREZ IXMATLAHUA MIRANDA</t>
   </si>
   <si>
+    <t>RAMIREZ SANCHEZ ULISES</t>
+  </si>
+  <si>
     <t>RICO ROSAS MAYRIN FERNANDA</t>
   </si>
   <si>
@@ -215,15 +227,15 @@
     <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
+  </si>
+  <si>
     <t>Ramírez Vargas Miranda Alejandra</t>
   </si>
   <si>
-    <t>Saucedo Rivalcoba Liliana Guadalupe</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -239,6 +251,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>VELASQUEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
+    <t>MARIA ELISA</t>
+  </si>
+  <si>
+    <t>ULISES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
@@ -254,15 +308,12 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -275,12 +326,15 @@
     <t>ESPARZA</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
@@ -294,12 +348,6 @@
   </si>
   <si>
     <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -664,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -828,10 +876,10 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -840,10 +888,10 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -905,10 +953,10 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -917,10 +965,10 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -982,10 +1030,10 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -994,13 +1042,13 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1059,10 +1107,10 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1071,16 +1119,16 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1136,10 +1184,10 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1148,10 +1196,10 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1166,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1213,10 +1261,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1225,16 +1273,16 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>10</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1243,7 +1291,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1281,7 +1329,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1290,10 +1338,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1302,10 +1350,10 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1317,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1367,10 +1415,10 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1379,16 +1427,16 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1408,40 +1456,40 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1453,31 +1501,31 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1485,46 +1533,46 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>10</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1533,28 +1581,28 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1565,43 +1613,43 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1610,28 +1658,28 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1639,46 +1687,46 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>8</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>7</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1687,28 +1735,28 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1716,22 +1764,22 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>10</v>
@@ -1740,22 +1788,22 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>10</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1764,28 +1812,28 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1793,46 +1841,46 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1841,28 +1889,28 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1870,46 +1918,46 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1918,22 +1966,22 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -1947,46 +1995,46 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -1995,25 +2043,25 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2024,46 +2072,46 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>6</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>7</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2072,28 +2120,28 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2104,28 +2152,28 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>10</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -2137,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2149,19 +2197,19 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2178,46 +2226,46 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>7</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2226,28 +2274,28 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2255,46 +2303,46 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>7</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2303,25 +2351,25 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2332,46 +2380,46 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2380,28 +2428,28 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2409,40 +2457,40 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2454,31 +2502,31 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2486,7 +2534,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2513,7 +2561,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -2522,10 +2570,10 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2534,22 +2582,22 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2569,40 +2617,40 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>10</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2611,28 +2659,28 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2640,40 +2688,40 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H28">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2685,31 +2733,31 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2717,10 +2765,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -2735,7 +2783,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2744,19 +2792,19 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2765,16 +2813,16 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2783,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2794,46 +2842,46 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2842,28 +2890,28 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2871,16 +2919,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -2889,16 +2937,16 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -2907,10 +2955,10 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2919,22 +2967,22 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -2948,16 +2996,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>6</v>
@@ -2966,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>7</v>
@@ -2978,16 +3026,16 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2996,16 +3044,16 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3014,10 +3062,10 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3025,46 +3073,46 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3073,28 +3121,28 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3102,46 +3150,46 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3150,28 +3198,28 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3179,46 +3227,46 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3227,28 +3275,28 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3256,46 +3304,46 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>6</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3304,28 +3352,28 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U36">
         <v>8</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3336,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -3345,10 +3393,10 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H37">
         <v>10</v>
@@ -3366,13 +3414,13 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3381,10 +3429,10 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3399,10 +3447,10 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3410,40 +3458,40 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="E38">
         <v>10</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38">
         <v>9</v>
       </c>
       <c r="H38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="I38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="J38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K38">
         <v>10</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3455,22 +3503,22 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3479,7 +3527,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3490,22 +3538,22 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>10</v>
       </c>
       <c r="G39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -3514,7 +3562,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -3526,7 +3574,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3535,28 +3583,28 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3564,34 +3612,34 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>6</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>8</v>
@@ -3603,7 +3651,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3612,25 +3660,25 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3641,46 +3689,46 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41">
         <v>9</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41">
         <v>7</v>
       </c>
       <c r="G41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H41">
         <v>10</v>
       </c>
       <c r="I41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K41">
         <v>10</v>
       </c>
       <c r="L41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -3689,10 +3737,10 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3701,16 +3749,16 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W41">
         <v>10</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3721,16 +3769,16 @@
         <v>10</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G42">
         <v>9</v>
@@ -3751,13 +3799,13 @@
         <v>10</v>
       </c>
       <c r="M42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -3766,10 +3814,10 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -3784,10 +3832,10 @@
         <v>10</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3795,75 +3843,383 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>9</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+      <c r="J43">
+        <v>9</v>
+      </c>
+      <c r="K43">
+        <v>9</v>
+      </c>
+      <c r="L43">
+        <v>10</v>
+      </c>
+      <c r="M43">
+        <v>10</v>
+      </c>
+      <c r="N43">
+        <v>-1</v>
+      </c>
+      <c r="O43">
+        <v>10</v>
+      </c>
+      <c r="P43">
+        <v>-1</v>
+      </c>
+      <c r="Q43">
+        <v>-1</v>
+      </c>
+      <c r="R43">
+        <v>10</v>
+      </c>
+      <c r="S43">
+        <v>10</v>
+      </c>
+      <c r="T43">
+        <v>10</v>
+      </c>
+      <c r="U43">
+        <v>9</v>
+      </c>
+      <c r="V43">
+        <v>9</v>
+      </c>
+      <c r="W43">
+        <v>9</v>
+      </c>
+      <c r="X43">
+        <v>10</v>
+      </c>
+      <c r="Y43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <v>9</v>
+      </c>
+      <c r="K44">
+        <v>10</v>
+      </c>
+      <c r="L44">
+        <v>8</v>
+      </c>
+      <c r="M44">
+        <v>8</v>
+      </c>
+      <c r="N44">
+        <v>-1</v>
+      </c>
+      <c r="O44">
+        <v>10</v>
+      </c>
+      <c r="P44">
+        <v>-1</v>
+      </c>
+      <c r="Q44">
+        <v>-1</v>
+      </c>
+      <c r="R44">
+        <v>9</v>
+      </c>
+      <c r="S44">
+        <v>8</v>
+      </c>
+      <c r="T44">
+        <v>10</v>
+      </c>
+      <c r="U44">
+        <v>10</v>
+      </c>
+      <c r="V44">
+        <v>10</v>
+      </c>
+      <c r="W44">
+        <v>10</v>
+      </c>
+      <c r="X44">
+        <v>8</v>
+      </c>
+      <c r="Y44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <v>9</v>
+      </c>
+      <c r="J45">
+        <v>7</v>
+      </c>
+      <c r="K45">
+        <v>10</v>
+      </c>
+      <c r="L45">
+        <v>8</v>
+      </c>
+      <c r="M45">
+        <v>8</v>
+      </c>
+      <c r="N45">
+        <v>-1</v>
+      </c>
+      <c r="O45">
+        <v>10</v>
+      </c>
+      <c r="P45">
+        <v>-1</v>
+      </c>
+      <c r="Q45">
+        <v>-1</v>
+      </c>
+      <c r="R45">
+        <v>9</v>
+      </c>
+      <c r="S45">
+        <v>8</v>
+      </c>
+      <c r="T45">
+        <v>10</v>
+      </c>
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45">
+        <v>7</v>
+      </c>
+      <c r="W45">
+        <v>10</v>
+      </c>
+      <c r="X45">
+        <v>8</v>
+      </c>
+      <c r="Y45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>9</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="I46">
+        <v>10</v>
+      </c>
+      <c r="J46">
+        <v>10</v>
+      </c>
+      <c r="K46">
+        <v>10</v>
+      </c>
+      <c r="L46">
+        <v>10</v>
+      </c>
+      <c r="M46">
+        <v>8</v>
+      </c>
+      <c r="N46">
+        <v>-1</v>
+      </c>
+      <c r="O46">
+        <v>9</v>
+      </c>
+      <c r="P46">
+        <v>-1</v>
+      </c>
+      <c r="Q46">
+        <v>-1</v>
+      </c>
+      <c r="R46">
+        <v>10</v>
+      </c>
+      <c r="S46">
+        <v>10</v>
+      </c>
+      <c r="T46">
+        <v>10</v>
+      </c>
+      <c r="U46">
+        <v>9</v>
+      </c>
+      <c r="V46">
+        <v>9</v>
+      </c>
+      <c r="W46">
+        <v>10</v>
+      </c>
+      <c r="X46">
+        <v>10</v>
+      </c>
+      <c r="Y46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47">
         <v>5</v>
       </c>
-      <c r="E43">
-        <v>7</v>
-      </c>
-      <c r="F43">
-        <v>6</v>
-      </c>
-      <c r="G43">
-        <v>6</v>
-      </c>
-      <c r="H43">
-        <v>10</v>
-      </c>
-      <c r="I43">
-        <v>6</v>
-      </c>
-      <c r="J43">
+      <c r="E47">
+        <v>7</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+      <c r="G47">
+        <v>6</v>
+      </c>
+      <c r="H47">
+        <v>10</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
         <v>5</v>
       </c>
-      <c r="K43">
-        <v>7</v>
-      </c>
-      <c r="L43">
-        <v>6</v>
-      </c>
-      <c r="M43">
-        <v>6</v>
-      </c>
-      <c r="N43">
-        <v>-1</v>
-      </c>
-      <c r="O43">
-        <v>-1</v>
-      </c>
-      <c r="P43">
-        <v>-1</v>
-      </c>
-      <c r="Q43">
-        <v>-1</v>
-      </c>
-      <c r="R43">
-        <v>-1</v>
-      </c>
-      <c r="S43">
-        <v>-1</v>
-      </c>
-      <c r="T43">
-        <v>10</v>
-      </c>
-      <c r="U43">
-        <v>6</v>
-      </c>
-      <c r="V43">
+      <c r="K47">
+        <v>7</v>
+      </c>
+      <c r="L47">
+        <v>6</v>
+      </c>
+      <c r="M47">
+        <v>6</v>
+      </c>
+      <c r="N47">
+        <v>-1</v>
+      </c>
+      <c r="O47">
+        <v>6</v>
+      </c>
+      <c r="P47">
+        <v>-1</v>
+      </c>
+      <c r="Q47">
+        <v>-1</v>
+      </c>
+      <c r="R47">
+        <v>6</v>
+      </c>
+      <c r="S47">
+        <v>6</v>
+      </c>
+      <c r="T47">
+        <v>10</v>
+      </c>
+      <c r="U47">
+        <v>6</v>
+      </c>
+      <c r="V47">
         <v>5</v>
       </c>
-      <c r="W43">
-        <v>7</v>
-      </c>
-      <c r="X43">
-        <v>6</v>
-      </c>
-      <c r="Y43">
+      <c r="W47">
+        <v>7</v>
+      </c>
+      <c r="X47">
+        <v>6</v>
+      </c>
+      <c r="Y47">
         <v>6</v>
       </c>
     </row>
@@ -3880,7 +4236,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3889,7 +4245,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3897,7 +4253,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3905,7 +4261,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -4018,16 +4374,16 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="O4">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>88</v>
+        <v>58.7</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4077,16 +4433,16 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>92.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O5">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P5">
         <v>88.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4136,22 +4492,22 @@
         <v>95</v>
       </c>
       <c r="N6">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
       <c r="O6">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>90.7</v>
       </c>
       <c r="Q6">
-        <v>92</v>
+        <v>61.3</v>
       </c>
       <c r="R6">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4195,22 +4551,22 @@
         <v>96.7</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O7">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7">
         <v>88.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="R7">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="S7">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4254,7 +4610,7 @@
         <v>98.3</v>
       </c>
       <c r="N8">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4263,13 +4619,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4313,16 +4669,16 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="O9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4372,7 +4728,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4381,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4431,7 +4787,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4440,7 +4796,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4454,16 +4810,16 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4472,40 +4828,40 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
-        <v>96.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4513,58 +4869,58 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D13">
         <v>100</v>
       </c>
       <c r="E13">
+        <v>92</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>85</v>
+      </c>
+      <c r="I13">
         <v>96</v>
       </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-      <c r="H13">
-        <v>92.5</v>
-      </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N13">
-        <v>92.5</v>
+        <v>87.3</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>96</v>
+        <v>62.7</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4575,7 +4931,7 @@
         <v>90</v>
       </c>
       <c r="C14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4590,17 +4946,17 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
         <v>96</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
-      <c r="K14">
-        <v>94</v>
-      </c>
       <c r="L14">
         <v>100</v>
       </c>
@@ -4608,16 +4964,16 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>93.7</v>
       </c>
       <c r="O14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4631,10 +4987,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C15">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4649,37 +5005,37 @@
         <v>100</v>
       </c>
       <c r="H15">
+        <v>90</v>
+      </c>
+      <c r="I15">
+        <v>96</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>94</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>93.7</v>
+      </c>
+      <c r="O15">
         <v>97.5</v>
       </c>
-      <c r="I15">
-        <v>98</v>
-      </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
-      <c r="K15">
-        <v>98</v>
-      </c>
-      <c r="L15">
-        <v>96.7</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>97.5</v>
-      </c>
-      <c r="O15">
-        <v>98</v>
-      </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>62.7</v>
       </c>
       <c r="R15">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4690,7 +5046,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C16">
         <v>96</v>
@@ -4699,7 +5055,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4708,7 +5064,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I16">
         <v>98</v>
@@ -4717,28 +5073,28 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>65.3</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4749,16 +5105,16 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4767,16 +5123,16 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="I17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J17">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4785,16 +5141,16 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>96</v>
+        <v>98.8</v>
       </c>
       <c r="P17">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>84</v>
+        <v>66.7</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4814,10 +5170,10 @@
         <v>92</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E18">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4826,16 +5182,16 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I18">
         <v>96</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K18">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4844,19 +5200,19 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>85</v>
+        <v>87.3</v>
       </c>
       <c r="O18">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4867,16 +5223,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D19">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -4885,40 +5241,40 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J19">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P19">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>96</v>
+        <v>62.7</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="S19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4926,16 +5282,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C20">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -4947,37 +5303,37 @@
         <v>87.5</v>
       </c>
       <c r="I20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="K20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N20">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="Q20">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4985,10 +5341,10 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C21">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -5006,13 +5362,13 @@
         <v>87.5</v>
       </c>
       <c r="I21">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5021,16 +5377,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>87.5</v>
+        <v>90.5</v>
       </c>
       <c r="O21">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>96</v>
+        <v>61.3</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5047,14 +5403,14 @@
         <v>95</v>
       </c>
       <c r="C22">
+        <v>96</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22">
         <v>92</v>
       </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
-      <c r="E22">
-        <v>100</v>
-      </c>
       <c r="F22">
         <v>100</v>
       </c>
@@ -5062,17 +5418,17 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>97.5</v>
+        <v>87.5</v>
       </c>
       <c r="I22">
+        <v>98</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>96</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
       <c r="L22">
         <v>100</v>
       </c>
@@ -5080,16 +5436,16 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>97.5</v>
+        <v>87.3</v>
       </c>
       <c r="O22">
-        <v>96</v>
+        <v>98.8</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5103,58 +5459,58 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C23">
+        <v>92</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>97.5</v>
+      </c>
+      <c r="I23">
         <v>96</v>
       </c>
-      <c r="D23">
-        <v>100</v>
-      </c>
-      <c r="E23">
-        <v>96</v>
-      </c>
-      <c r="F23">
-        <v>100</v>
-      </c>
-      <c r="G23">
-        <v>100</v>
-      </c>
-      <c r="H23">
-        <v>87.5</v>
-      </c>
-      <c r="I23">
-        <v>98</v>
-      </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="N23">
-        <v>87.5</v>
+        <v>96.8</v>
       </c>
       <c r="O23">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5162,16 +5518,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C24">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D24">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5180,40 +5536,40 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I24">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J24">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="N24">
-        <v>85</v>
+        <v>90.5</v>
       </c>
       <c r="O24">
-        <v>86</v>
+        <v>98.8</v>
       </c>
       <c r="P24">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5221,13 +5577,13 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5239,40 +5595,40 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>92.5</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>92.5</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="S25">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5289,7 +5645,7 @@
         <v>78.3</v>
       </c>
       <c r="E26">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5298,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="I26">
         <v>86</v>
@@ -5316,22 +5672,22 @@
         <v>95</v>
       </c>
       <c r="N26">
-        <v>82.5</v>
+        <v>87.3</v>
       </c>
       <c r="O26">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="P26">
         <v>86</v>
       </c>
       <c r="Q26">
-        <v>88</v>
+        <v>58.7</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S26">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5366,16 +5722,16 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M27">
         <v>95</v>
       </c>
       <c r="N27">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5384,13 +5740,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5398,13 +5754,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5416,16 +5772,16 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5434,19 +5790,19 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5460,13 +5816,13 @@
         <v>85</v>
       </c>
       <c r="C29">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D29">
         <v>78.3</v>
       </c>
       <c r="E29">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -5475,40 +5831,40 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="I29">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J29">
         <v>86</v>
       </c>
       <c r="K29">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M29">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="N29">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O29">
-        <v>98</v>
+        <v>91.3</v>
       </c>
       <c r="P29">
         <v>86</v>
       </c>
       <c r="Q29">
-        <v>94</v>
+        <v>58.7</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S29">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5516,16 +5872,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C30">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D30">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -5534,40 +5890,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>72.5</v>
+        <v>92.5</v>
       </c>
       <c r="I30">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L30">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>95</v>
       </c>
       <c r="N30">
-        <v>72.5</v>
+        <v>95.2</v>
       </c>
       <c r="O30">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>88</v>
+        <v>65.3</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5575,58 +5931,58 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="C31">
+        <v>84</v>
+      </c>
+      <c r="D31">
+        <v>78.3</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <v>85</v>
+      </c>
+      <c r="I31">
         <v>92</v>
       </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
-      <c r="E31">
-        <v>100</v>
-      </c>
-      <c r="F31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
-      <c r="H31">
-        <v>70</v>
-      </c>
-      <c r="I31">
-        <v>96</v>
-      </c>
       <c r="J31">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="K31">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>87.3</v>
+      </c>
+      <c r="O31">
         <v>95</v>
       </c>
-      <c r="M31">
-        <v>95</v>
-      </c>
-      <c r="N31">
-        <v>70</v>
-      </c>
-      <c r="O31">
-        <v>96</v>
-      </c>
       <c r="P31">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Q31">
-        <v>90</v>
+        <v>61.3</v>
       </c>
       <c r="R31">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5634,16 +5990,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C32">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D32">
         <v>78.3</v>
       </c>
       <c r="E32">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5652,40 +6008,40 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I32">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J32">
         <v>86</v>
       </c>
       <c r="K32">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L32">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="N32">
-        <v>70</v>
+        <v>85.7</v>
       </c>
       <c r="O32">
-        <v>86</v>
+        <v>98.8</v>
       </c>
       <c r="P32">
         <v>86</v>
       </c>
       <c r="Q32">
-        <v>82</v>
+        <v>62.7</v>
       </c>
       <c r="R32">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>95</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5693,58 +6049,58 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C33">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D33">
-        <v>82.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="E33">
+        <v>96</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>72.5</v>
+      </c>
+      <c r="I33">
         <v>92</v>
       </c>
-      <c r="F33">
-        <v>100</v>
-      </c>
-      <c r="G33">
-        <v>100</v>
-      </c>
-      <c r="H33">
-        <v>85</v>
-      </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
       <c r="J33">
-        <v>90.7</v>
+        <v>86</v>
       </c>
       <c r="K33">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M33">
         <v>95</v>
       </c>
       <c r="N33">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P33">
-        <v>90.7</v>
+        <v>86</v>
       </c>
       <c r="Q33">
-        <v>92</v>
+        <v>58.7</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S33">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5752,58 +6108,58 @@
         <v>42</v>
       </c>
       <c r="B34">
+        <v>55</v>
+      </c>
+      <c r="C34">
+        <v>92</v>
+      </c>
+      <c r="D34">
+        <v>100</v>
+      </c>
+      <c r="E34">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>70</v>
+      </c>
+      <c r="I34">
+        <v>96</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>90</v>
+      </c>
+      <c r="L34">
         <v>95</v>
       </c>
-      <c r="C34">
-        <v>100</v>
-      </c>
-      <c r="D34">
-        <v>100</v>
-      </c>
-      <c r="E34">
-        <v>100</v>
-      </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>100</v>
-      </c>
-      <c r="H34">
+      <c r="M34">
+        <v>95</v>
+      </c>
+      <c r="N34">
+        <v>81</v>
+      </c>
+      <c r="O34">
         <v>97.5</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
-      <c r="K34">
-        <v>96</v>
-      </c>
-      <c r="L34">
-        <v>100</v>
-      </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
-      <c r="N34">
-        <v>97.5</v>
-      </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5811,16 +6167,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="C35">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5829,40 +6185,40 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>97.5</v>
+        <v>70</v>
       </c>
       <c r="I35">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N35">
-        <v>97.5</v>
+        <v>44.4</v>
       </c>
       <c r="O35">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5870,16 +6226,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D36">
-        <v>100</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E36">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -5891,37 +6247,37 @@
         <v>85</v>
       </c>
       <c r="I36">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="K36">
         <v>92</v>
       </c>
       <c r="L36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>95</v>
       </c>
       <c r="N36">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="O36">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="Q36">
-        <v>92</v>
+        <v>61.3</v>
       </c>
       <c r="R36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5938,7 +6294,7 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -5947,7 +6303,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -5956,7 +6312,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -5965,7 +6321,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>95</v>
+        <v>61.9</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -5974,7 +6330,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -5988,16 +6344,16 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -6006,16 +6362,16 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -6024,19 +6380,19 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6050,7 +6406,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -6068,13 +6424,13 @@
         <v>97.5</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6083,16 +6439,16 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>97.5</v>
+        <v>61.9</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="P39">
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>96</v>
+        <v>66.7</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6106,58 +6462,58 @@
         <v>48</v>
       </c>
       <c r="B40">
+        <v>85</v>
+      </c>
+      <c r="C40">
+        <v>96</v>
+      </c>
+      <c r="D40">
+        <v>100</v>
+      </c>
+      <c r="E40">
+        <v>88</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <v>85</v>
+      </c>
+      <c r="I40">
+        <v>98</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>92</v>
+      </c>
+      <c r="L40">
         <v>95</v>
       </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-      <c r="D40">
-        <v>100</v>
-      </c>
-      <c r="E40">
-        <v>100</v>
-      </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40">
+      <c r="M40">
         <v>95</v>
       </c>
-      <c r="I40">
-        <v>100</v>
-      </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
-      <c r="L40">
-        <v>96.7</v>
-      </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
       <c r="N40">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>61.3</v>
       </c>
       <c r="R40">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6174,7 +6530,7 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -6183,7 +6539,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -6192,16 +6548,16 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L41">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M41">
         <v>100</v>
       </c>
       <c r="N41">
-        <v>97.5</v>
+        <v>60.3</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6210,10 +6566,10 @@
         <v>100</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>62.7</v>
       </c>
       <c r="R41">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6224,10 +6580,10 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>100</v>
@@ -6242,10 +6598,10 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="I42">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J42">
         <v>100</v>
@@ -6260,16 +6616,16 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>87.5</v>
+        <v>63.5</v>
       </c>
       <c r="O42">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P42">
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -6283,58 +6639,294 @@
         <v>51</v>
       </c>
       <c r="B43">
+        <v>100</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+      <c r="D43">
+        <v>100</v>
+      </c>
+      <c r="E43">
+        <v>100</v>
+      </c>
+      <c r="F43">
+        <v>100</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <v>97.5</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <v>96</v>
+      </c>
+      <c r="L43">
+        <v>100</v>
+      </c>
+      <c r="M43">
+        <v>100</v>
+      </c>
+      <c r="N43">
+        <v>61.9</v>
+      </c>
+      <c r="O43">
+        <v>100</v>
+      </c>
+      <c r="P43">
+        <v>100</v>
+      </c>
+      <c r="Q43">
+        <v>64</v>
+      </c>
+      <c r="R43">
+        <v>100</v>
+      </c>
+      <c r="S43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44">
+        <v>95</v>
+      </c>
+      <c r="C44">
+        <v>100</v>
+      </c>
+      <c r="D44">
+        <v>100</v>
+      </c>
+      <c r="E44">
+        <v>100</v>
+      </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <v>95</v>
+      </c>
+      <c r="I44">
+        <v>100</v>
+      </c>
+      <c r="J44">
+        <v>100</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="L44">
+        <v>96.7</v>
+      </c>
+      <c r="M44">
+        <v>100</v>
+      </c>
+      <c r="N44">
+        <v>60.3</v>
+      </c>
+      <c r="O44">
+        <v>100</v>
+      </c>
+      <c r="P44">
+        <v>100</v>
+      </c>
+      <c r="Q44">
+        <v>66.7</v>
+      </c>
+      <c r="R44">
+        <v>95.8</v>
+      </c>
+      <c r="S44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <v>95</v>
+      </c>
+      <c r="C45">
+        <v>100</v>
+      </c>
+      <c r="D45">
+        <v>100</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
+      </c>
+      <c r="H45">
+        <v>97.5</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45">
+        <v>100</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>96.7</v>
+      </c>
+      <c r="M45">
+        <v>100</v>
+      </c>
+      <c r="N45">
+        <v>61.9</v>
+      </c>
+      <c r="O45">
+        <v>100</v>
+      </c>
+      <c r="P45">
+        <v>100</v>
+      </c>
+      <c r="Q45">
+        <v>66.7</v>
+      </c>
+      <c r="R45">
+        <v>95.8</v>
+      </c>
+      <c r="S45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46">
+        <v>85</v>
+      </c>
+      <c r="C46">
+        <v>96</v>
+      </c>
+      <c r="D46">
+        <v>100</v>
+      </c>
+      <c r="E46">
+        <v>96</v>
+      </c>
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46">
+        <v>87.5</v>
+      </c>
+      <c r="I46">
+        <v>98</v>
+      </c>
+      <c r="J46">
+        <v>100</v>
+      </c>
+      <c r="K46">
+        <v>96</v>
+      </c>
+      <c r="L46">
+        <v>100</v>
+      </c>
+      <c r="M46">
+        <v>100</v>
+      </c>
+      <c r="N46">
+        <v>55.6</v>
+      </c>
+      <c r="O46">
+        <v>98.8</v>
+      </c>
+      <c r="P46">
+        <v>100</v>
+      </c>
+      <c r="Q46">
+        <v>64</v>
+      </c>
+      <c r="R46">
+        <v>100</v>
+      </c>
+      <c r="S46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47">
         <v>90</v>
       </c>
-      <c r="C43">
+      <c r="C47">
         <v>96</v>
       </c>
-      <c r="D43">
+      <c r="D47">
         <v>78.3</v>
       </c>
-      <c r="E43">
+      <c r="E47">
         <v>84</v>
       </c>
-      <c r="F43">
-        <v>100</v>
-      </c>
-      <c r="G43">
-        <v>100</v>
-      </c>
-      <c r="H43">
+      <c r="F47">
+        <v>100</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47">
         <v>95</v>
       </c>
-      <c r="I43">
+      <c r="I47">
         <v>98</v>
       </c>
-      <c r="J43">
+      <c r="J47">
         <v>86</v>
       </c>
-      <c r="K43">
+      <c r="K47">
         <v>82</v>
       </c>
-      <c r="L43">
+      <c r="L47">
         <v>95</v>
       </c>
-      <c r="M43">
+      <c r="M47">
         <v>95</v>
       </c>
-      <c r="N43">
-        <v>95</v>
-      </c>
-      <c r="O43">
-        <v>98</v>
-      </c>
-      <c r="P43">
+      <c r="N47">
+        <v>60.3</v>
+      </c>
+      <c r="O47">
+        <v>98.8</v>
+      </c>
+      <c r="P47">
         <v>86</v>
       </c>
-      <c r="Q43">
-        <v>82</v>
-      </c>
-      <c r="R43">
-        <v>95</v>
-      </c>
-      <c r="S43">
-        <v>95</v>
+      <c r="Q47">
+        <v>54.7</v>
+      </c>
+      <c r="R47">
+        <v>94.8</v>
+      </c>
+      <c r="S47">
+        <v>94.8</v>
       </c>
     </row>
   </sheetData>
@@ -6362,31 +6954,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6394,10 +6986,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>32</v>
@@ -6406,51 +6998,51 @@
         <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="H2">
         <v>7.3</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6458,10 +7050,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -6470,33 +7062,33 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6508,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6522,13 +7114,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6540,7 +7132,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6554,13 +7146,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6572,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6588,7 +7180,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6597,22 +7189,262 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920058</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920058</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920058</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920067</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920067</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>22330051920067</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>22330051920335</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>22330051920335</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>22330051920335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>22330051920076</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>22330051920076</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>22330051920076</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -6622,7 +7454,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6631,22 +7463,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6654,185 +7486,507 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920212</v>
+        <v>22330051920058</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920359</v>
+        <v>22330051920058</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920237</v>
+        <v>22330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920071</v>
+        <v>22330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920218</v>
+        <v>22330051920067</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920053</v>
+        <v>22330051920067</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920242</v>
+        <v>22330051920335</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>22330051920335</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920076</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920076</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920076</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920053</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920053</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920242</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920242</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920212</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920359</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920237</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920071</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920218</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
         <v>22330051920084</v>
       </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -3263,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>5</v>
@@ -3340,7 +3340,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -3417,7 +3417,7 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -3571,7 +3571,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>8</v>
@@ -3725,7 +3725,7 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
         <v>9</v>
@@ -3802,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
         <v>10</v>
@@ -3879,7 +3879,7 @@
         <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
         <v>10</v>
@@ -3956,7 +3956,7 @@
         <v>8</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>10</v>
@@ -4033,7 +4033,7 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
         <v>10</v>
@@ -4110,7 +4110,7 @@
         <v>8</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O46">
         <v>9</v>
@@ -4187,7 +4187,7 @@
         <v>6</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -6203,7 +6203,7 @@
         <v>95</v>
       </c>
       <c r="N35">
-        <v>44.4</v>
+        <v>81</v>
       </c>
       <c r="O35">
         <v>91.3</v>
@@ -6262,7 +6262,7 @@
         <v>95</v>
       </c>
       <c r="N36">
-        <v>54</v>
+        <v>90.5</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -6321,7 +6321,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>61.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -6439,7 +6439,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>61.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O39">
         <v>96.3</v>
@@ -6498,7 +6498,7 @@
         <v>95</v>
       </c>
       <c r="N40">
-        <v>54</v>
+        <v>85.7</v>
       </c>
       <c r="O40">
         <v>98.8</v>
@@ -6557,7 +6557,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>60.3</v>
+        <v>95.2</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6616,7 +6616,7 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>63.5</v>
+        <v>100</v>
       </c>
       <c r="O42">
         <v>100</v>
@@ -6675,7 +6675,7 @@
         <v>100</v>
       </c>
       <c r="N43">
-        <v>61.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O43">
         <v>100</v>
@@ -6734,7 +6734,7 @@
         <v>100</v>
       </c>
       <c r="N44">
-        <v>60.3</v>
+        <v>96.8</v>
       </c>
       <c r="O44">
         <v>100</v>
@@ -6793,7 +6793,7 @@
         <v>100</v>
       </c>
       <c r="N45">
-        <v>61.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O45">
         <v>100</v>
@@ -6852,7 +6852,7 @@
         <v>100</v>
       </c>
       <c r="N46">
-        <v>55.6</v>
+        <v>90.5</v>
       </c>
       <c r="O46">
         <v>98.8</v>
@@ -6911,7 +6911,7 @@
         <v>95</v>
       </c>
       <c r="N47">
-        <v>60.3</v>
+        <v>95.2</v>
       </c>
       <c r="O47">
         <v>98.8</v>

--- a/grupos/5ARHM - Estadisticos 20241.xlsx
+++ b/grupos/5ARHM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -230,12 +230,12 @@
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Liliana Guadalupe</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -251,49 +251,16 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MARIA ELISA</t>
-  </si>
-  <si>
-    <t>ULISES</t>
-  </si>
-  <si>
     <t>OREA</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>GUERRA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -302,6 +269,9 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -314,10 +284,13 @@
     <t>RANGEL</t>
   </si>
   <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
@@ -335,7 +308,10 @@
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>CLAUDIA PAOLA</t>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -344,7 +320,7 @@
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
+    <t>JIMENA</t>
   </si>
   <si>
     <t>ANGELES VALERIA</t>
@@ -882,10 +858,10 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -900,10 +876,10 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -959,10 +935,10 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -977,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1036,10 +1012,10 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1057,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1113,10 +1089,10 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1131,10 +1107,10 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1190,10 +1166,10 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1267,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -1285,7 +1261,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1344,10 +1320,10 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1421,10 +1397,10 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1439,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1456,13 +1432,13 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1474,13 +1450,13 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1492,13 +1468,13 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1510,13 +1486,13 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1575,10 +1551,10 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1652,10 +1628,10 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1729,10 +1705,10 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1747,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1806,10 +1782,10 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -1883,10 +1859,10 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -1901,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -1960,10 +1936,10 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -1978,7 +1954,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2037,10 +2013,10 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2055,7 +2031,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2114,10 +2090,10 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -2191,10 +2167,10 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -2212,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2268,10 +2244,10 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>8</v>
@@ -2345,10 +2321,10 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2363,10 +2339,10 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2422,10 +2398,10 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2443,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2457,13 +2433,13 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2475,13 +2451,13 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -2493,13 +2469,13 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2511,13 +2487,13 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2576,10 +2552,10 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>6</v>
@@ -2597,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2653,10 +2629,10 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -2671,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2688,13 +2664,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -2706,13 +2682,13 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>10</v>
@@ -2724,13 +2700,13 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2742,13 +2718,13 @@
         <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2807,10 +2783,10 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2828,7 +2804,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2884,10 +2860,10 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -2961,10 +2937,10 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -3038,10 +3014,10 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -3115,10 +3091,10 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>6</v>
@@ -3136,7 +3112,7 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3192,10 +3168,10 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>6</v>
@@ -3269,10 +3245,10 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>6</v>
@@ -3290,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3346,10 +3322,10 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -3367,7 +3343,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3423,10 +3399,10 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -3441,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3458,13 +3434,13 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>10</v>
@@ -3476,13 +3452,13 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>10</v>
@@ -3494,13 +3470,13 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -3512,13 +3488,13 @@
         <v>9</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3577,10 +3553,10 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>10</v>
@@ -3595,7 +3571,7 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -3654,10 +3630,10 @@
         <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
         <v>9</v>
@@ -3731,10 +3707,10 @@
         <v>9</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>10</v>
@@ -3808,10 +3784,10 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
@@ -3885,10 +3861,10 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>10</v>
@@ -3962,10 +3938,10 @@
         <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
         <v>9</v>
@@ -3980,7 +3956,7 @@
         <v>10</v>
       </c>
       <c r="V44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W44">
         <v>10</v>
@@ -4039,10 +4015,10 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
         <v>9</v>
@@ -4116,10 +4092,10 @@
         <v>9</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R46">
         <v>10</v>
@@ -4134,7 +4110,7 @@
         <v>9</v>
       </c>
       <c r="V46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W46">
         <v>10</v>
@@ -4193,10 +4169,10 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R47">
         <v>6</v>
@@ -4214,7 +4190,7 @@
         <v>5</v>
       </c>
       <c r="W47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X47">
         <v>6</v>
@@ -4380,10 +4356,10 @@
         <v>98.8</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>58.7</v>
+        <v>88.8</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4439,10 +4415,10 @@
         <v>98.8</v>
       </c>
       <c r="P5">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q5">
-        <v>60</v>
+        <v>87.5</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4498,10 +4474,10 @@
         <v>97.5</v>
       </c>
       <c r="P6">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
       <c r="Q6">
-        <v>61.3</v>
+        <v>92.5</v>
       </c>
       <c r="R6">
         <v>97.90000000000001</v>
@@ -4557,10 +4533,10 @@
         <v>98.8</v>
       </c>
       <c r="P7">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q7">
-        <v>64</v>
+        <v>88.8</v>
       </c>
       <c r="R7">
         <v>94.8</v>
@@ -4619,7 +4595,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4678,7 +4654,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>64</v>
+        <v>91.3</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4737,7 +4713,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>66.7</v>
+        <v>97.5</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4796,7 +4772,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>66.7</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4810,13 +4786,13 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -4828,13 +4804,13 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -4846,16 +4822,16 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
         <v>93.8</v>
@@ -4911,10 +4887,10 @@
         <v>97.5</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q13">
-        <v>62.7</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4973,7 +4949,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5032,7 +5008,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>62.7</v>
+        <v>93.8</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -5091,7 +5067,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>65.3</v>
+        <v>96.3</v>
       </c>
       <c r="R16">
         <v>95.8</v>
@@ -5150,7 +5126,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -5206,10 +5182,10 @@
         <v>97.5</v>
       </c>
       <c r="P18">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q18">
-        <v>56</v>
+        <v>83.8</v>
       </c>
       <c r="R18">
         <v>95.8</v>
@@ -5265,10 +5241,10 @@
         <v>97.5</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>62.7</v>
+        <v>90</v>
       </c>
       <c r="R19">
         <v>95.8</v>
@@ -5324,10 +5300,10 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
       <c r="Q20">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
         <v>97.90000000000001</v>
@@ -5386,7 +5362,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>61.3</v>
+        <v>86.3</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5445,7 +5421,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5501,10 +5477,10 @@
         <v>97.5</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q23">
-        <v>66.7</v>
+        <v>96.3</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5563,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>60</v>
+        <v>88.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5577,13 +5553,13 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5595,13 +5571,13 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5613,16 +5589,16 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R25">
         <v>93.8</v>
@@ -5678,10 +5654,10 @@
         <v>91.3</v>
       </c>
       <c r="P26">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>58.7</v>
+        <v>83.8</v>
       </c>
       <c r="R26">
         <v>90.59999999999999</v>
@@ -5737,10 +5713,10 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q27">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="R27">
         <v>97.90000000000001</v>
@@ -5754,13 +5730,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5772,13 +5748,13 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -5790,16 +5766,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R28">
         <v>93.8</v>
@@ -5855,10 +5831,10 @@
         <v>91.3</v>
       </c>
       <c r="P29">
-        <v>86</v>
+        <v>87.5</v>
       </c>
       <c r="Q29">
-        <v>58.7</v>
+        <v>83.8</v>
       </c>
       <c r="R29">
         <v>90.59999999999999</v>
@@ -5917,7 +5893,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>65.3</v>
+        <v>96.3</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5973,10 +5949,10 @@
         <v>95</v>
       </c>
       <c r="P31">
-        <v>86</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q31">
-        <v>61.3</v>
+        <v>91.3</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -6032,10 +6008,10 @@
         <v>98.8</v>
       </c>
       <c r="P32">
-        <v>86</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q32">
-        <v>62.7</v>
+        <v>90</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6091,10 +6067,10 @@
         <v>95</v>
       </c>
       <c r="P33">
-        <v>86</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q33">
-        <v>58.7</v>
+        <v>83.8</v>
       </c>
       <c r="R33">
         <v>90.59999999999999</v>
@@ -6153,7 +6129,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>60</v>
+        <v>86.3</v>
       </c>
       <c r="R34">
         <v>90.59999999999999</v>
@@ -6209,10 +6185,10 @@
         <v>91.3</v>
       </c>
       <c r="P35">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q35">
-        <v>54.7</v>
+        <v>83.8</v>
       </c>
       <c r="R35">
         <v>90.59999999999999</v>
@@ -6268,10 +6244,10 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>90.7</v>
+        <v>92.2</v>
       </c>
       <c r="Q36">
-        <v>61.3</v>
+        <v>85</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -6330,7 +6306,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>64</v>
+        <v>96.3</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -6344,13 +6320,13 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -6362,13 +6338,13 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -6380,16 +6356,16 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R38">
         <v>93.8</v>
@@ -6448,7 +6424,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6504,10 +6480,10 @@
         <v>98.8</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q40">
-        <v>61.3</v>
+        <v>87.5</v>
       </c>
       <c r="R40">
         <v>96.90000000000001</v>
@@ -6566,7 +6542,7 @@
         <v>100</v>
       </c>
       <c r="Q41">
-        <v>62.7</v>
+        <v>95</v>
       </c>
       <c r="R41">
         <v>100</v>
@@ -6625,7 +6601,7 @@
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -6684,7 +6660,7 @@
         <v>100</v>
       </c>
       <c r="Q43">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="R43">
         <v>100</v>
@@ -6743,7 +6719,7 @@
         <v>100</v>
       </c>
       <c r="Q44">
-        <v>66.7</v>
+        <v>98.8</v>
       </c>
       <c r="R44">
         <v>95.8</v>
@@ -6799,10 +6775,10 @@
         <v>100</v>
       </c>
       <c r="P45">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q45">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R45">
         <v>95.8</v>
@@ -6858,10 +6834,10 @@
         <v>98.8</v>
       </c>
       <c r="P46">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q46">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="R46">
         <v>100</v>
@@ -6917,10 +6893,10 @@
         <v>98.8</v>
       </c>
       <c r="P47">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q47">
-        <v>54.7</v>
+        <v>83.8</v>
       </c>
       <c r="R47">
         <v>94.8</v>
@@ -6992,25 +6968,25 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>72.7</v>
+        <v>77.3</v>
       </c>
       <c r="G2" s="2">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
       <c r="H2">
         <v>7.3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7024,30 +7000,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="G3" s="2">
         <v>4.5</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
@@ -7056,30 +7032,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>97.7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.3</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4" s="2">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="J4" s="2">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4" s="2">
-        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
@@ -7100,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7180,7 +7156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7207,246 +7183,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920058</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920058</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920058</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920067</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920067</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920067</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920335</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920335</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920335</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920076</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920076</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920076</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7454,7 +7190,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7486,131 +7222,131 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920058</v>
+        <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920058</v>
+        <v>21330051920053</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920058</v>
+        <v>21330051920053</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920067</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920067</v>
+        <v>21330051920242</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920067</v>
+        <v>22330051920423</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7619,67 +7355,67 @@
         <v>68</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920335</v>
+        <v>22330051920334</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920335</v>
+        <v>21330051920359</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920335</v>
+        <v>21330051920237</v>
       </c>
       <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -7688,67 +7424,67 @@
         <v>68</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920076</v>
+        <v>22330051920068</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920076</v>
+        <v>22330051920071</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920076</v>
+        <v>22330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7757,236 +7493,29 @@
         <v>68</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920053</v>
+        <v>22330051920084</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
         <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920053</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920242</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920242</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920212</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920359</v>
-      </c>
-      <c r="B19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920237</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920071</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920218</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920084</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>
